--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>47</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2257</v>
+        <v>3003</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1641</v>
+        <v>2214</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1627</v>
+        <v>2115</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>384</v>
+        <v>493</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>263</v>
+        <v>380</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>336</v>
+        <v>391</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>508</v>
+        <v>684</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>300</v>
+        <v>377</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>395</v>
+        <v>562</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>225</v>
+        <v>286</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>130</v>
+        <v>237</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>307</v>
+        <v>386</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>175</v>
+        <v>233</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>169</v>
+        <v>226</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>208</v>
+        <v>274</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="J14" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>184</v>
+      </c>
+      <c r="M14" s="12" t="n">
         <v>78</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="L14" s="12" t="n">
-        <v>141</v>
-      </c>
-      <c r="M14" s="12" t="n">
-        <v>60</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>229</v>
+        <v>322</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>225</v>
+        <v>307</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>190</v>
+        <v>236</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,104 +1180,104 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>72</v>
+        <v>214</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>11</v>
+        <v>128</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,35 +1307,35 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F22" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="I22" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="G22" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="J22" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,89 +1465,89 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="H23" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="K23" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="L23" s="12" t="n">
-        <v>55</v>
+        <v>117</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,89 +1573,89 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1685,47 +1685,47 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06403</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GUASTALLA</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>06403</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>GUASTALLA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="M29" s="12" t="n">
         <v>40</v>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>21</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,35 +1843,35 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1955,31 +1955,31 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F32" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="J32" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,35 +2005,35 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,39 +2059,39 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G34" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H34" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="L34" s="12" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2117,47 +2117,47 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2171,47 +2171,47 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="L36" s="12" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2260,12 +2260,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="G38" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H38" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="L38" s="12" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,32 +2329,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G39" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J39" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H39" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="K39" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>2</v>
@@ -2368,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,51 +2383,51 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,35 +2437,35 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J41" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="J41" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="K41" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2476,12 +2476,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,51 +2491,51 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,35 +2545,35 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J43" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2599,51 +2599,51 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="G44" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F44" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="G44" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H44" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05512</t>
+          <t>05589</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN PIETRO TERME</t>
+          <t>ZOLA PREDOSA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2657,47 +2657,47 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05589</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ZOLA PREDOSA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,143 +2707,143 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>05512</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
+          <t>CASTEL SAN PIETRO TERME</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H47" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I47" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J47" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J47" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="K47" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+          <t>BOMPORTO</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I48" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J48" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L48" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M48" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="M48" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0</v>
@@ -3026,13 +3026,13 @@
         <v>0</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="12" t="n">
         <v>0</v>
@@ -3184,13 +3184,13 @@
         <v>0</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I55" s="12" t="n">
         <v>0</v>
@@ -3238,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="12" t="n">
         <v>0</v>
@@ -3292,13 +3292,13 @@
         <v>0</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>562</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.300711743772242</v>
+        <v>169</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>234</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.03846153846153846</v>
+        <v>9</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>274</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.0218978102189781</v>
+        <v>6</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>184</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.4239130434782609</v>
+        <v>78</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>322</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.04968944099378882</v>
+        <v>16</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>184</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.05434782608695652</v>
+        <v>10</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>237</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.008438818565400843</v>
+        <v>2</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>214</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3551401869158878</v>
+        <v>76</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>90</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.2222222222222222</v>
+        <v>20</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>90</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.07777777777777778</v>
+        <v>7</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>70</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1285714285714286</v>
+        <v>9</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>138</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.01449275362318841</v>
+        <v>2</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>117</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.3675213675213675</v>
+        <v>43</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>101</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.2277227722772277</v>
+        <v>23</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>114</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.008771929824561403</v>
+        <v>1</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>81</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.06172839506172839</v>
+        <v>5</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>86</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.2674418604651163</v>
+        <v>23</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>76</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.0131578947368421</v>
+        <v>1</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>68</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.5882352941176471</v>
+        <v>40</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>65</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0.03076923076923077</v>
+        <v>2</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>53</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.6792452830188679</v>
+        <v>36</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>35</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0.1142857142857143</v>
+        <v>4</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>59</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0.1525423728813559</v>
+        <v>9</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>78</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0.2307692307692308</v>
+        <v>18</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>42</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0.04761904761904762</v>
+        <v>2</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>92</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0.02173913043478261</v>
+        <v>2</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>75</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0.02666666666666667</v>
+        <v>2</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>69</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0.04347826086956522</v>
+        <v>3</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>57</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0.01754385964912281</v>
+        <v>1</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>45</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>0.2444444444444444</v>
+        <v>11</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>55</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>0.1454545454545454</v>
+        <v>8</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>95</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0.01052631578947368</v>
+        <v>1</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>42</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>0.02380952380952381</v>
+        <v>1</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>16</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>47</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3003</v>
+        <v>3185</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2214</v>
+        <v>2357</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2115</v>
+        <v>2240</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>380</v>
+        <v>413</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>684</v>
+        <v>736</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>562</v>
+        <v>607</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>42</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>6</v>
@@ -983,35 +983,35 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>38</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>2</v>
@@ -1049,16 +1049,16 @@
         <v>19</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>16</v>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>37</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>10</v>
@@ -1145,47 +1145,47 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,35 +1195,35 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>214</v>
+        <v>93</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1234,50 +1234,50 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,54 +1288,54 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1415,19 +1415,19 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>12</v>
@@ -1436,7 +1436,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>2</v>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,47 +1523,47 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>71</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,143 +1573,143 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F25" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="G25" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="H25" s="12" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>14</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>14</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1739,28 +1739,28 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>60</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>51</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>29</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>1</v>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>20</v>
@@ -1814,10 +1814,10 @@
         <v>9</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1847,19 +1847,19 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>12</v>
@@ -1868,14 +1868,14 @@
         <v>21</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1901,31 +1901,31 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>21</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,35 +1951,35 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2009,31 +2009,31 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J34" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="M34" s="12" t="n">
         <v>10</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>18</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2117,47 +2117,47 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,35 +2167,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
         <v>35</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J36" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="M36" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,12 +2206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J38" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K38" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="L38" s="12" t="n">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,35 +2329,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="G39" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2368,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,35 +2383,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="G40" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I40" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="H40" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="J40" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2441,19 +2441,19 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>10</v>
@@ -2462,10 +2462,10 @@
         <v>4</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2476,12 +2476,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,51 +2491,51 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>6</v>
@@ -2678,14 +2678,14 @@
         <v>0</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
         <v>6</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>1</v>
@@ -2768,7 +2768,7 @@
         <v>11</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>0</v>
@@ -2836,10 +2836,10 @@
         <v>4</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0</v>
@@ -3026,13 +3026,13 @@
         <v>0</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>0</v>
@@ -3292,13 +3292,13 @@
         <v>0</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -525,7 +525,7 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -1026,11 +1026,7 @@
           <t>PIACENZA</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>GIURICIN ANTONIO</t>
@@ -2808,7 +2804,11 @@
           <t>BOMPORTO</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
           <t>LIBANORI FEDERICO</t>
@@ -2858,11 +2858,7 @@
           <t>PARMA</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+      <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t>IACONA GIOVANNI</t>
@@ -2912,7 +2908,11 @@
           <t>FIDENZA</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>IACONA GIOVANNI</t>
@@ -2962,7 +2962,11 @@
           <t>MEDICINA</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
@@ -3120,7 +3124,11 @@
           <t>PIANORO</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
@@ -3278,11 +3286,7 @@
           <t>PIACENZA</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="inlineStr">
         <is>
           <t>GIURICIN ANTONIO</t>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>47</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3185</v>
+        <v>3352</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2357</v>
+        <v>2488</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2240</v>
+        <v>2362</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>515</v>
+        <v>537</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H13" s="12" t="n">
+        <v>167</v>
+      </c>
+      <c r="I13" s="12" t="n">
         <v>144</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>141</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>42</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>6</v>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1033,28 +1033,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>16</v>
@@ -1087,31 +1087,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1141,28 +1141,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>32</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>2</v>
@@ -1176,54 +1176,54 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1249,31 +1249,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>32</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1284,54 +1284,54 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1357,31 +1357,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1392,12 +1392,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1407,51 +1407,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1461,51 +1461,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1515,35 +1515,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1554,12 +1554,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1569,143 +1569,143 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>71</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1735,28 +1735,28 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>1</v>
@@ -1789,16 +1789,16 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>44</v>
@@ -1807,10 +1807,10 @@
         <v>20</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>41</v>
@@ -1843,19 +1843,19 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>34</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>12</v>
@@ -1864,7 +1864,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>2</v>
@@ -1900,13 +1900,13 @@
         <v>49</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>33</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>43</v>
@@ -1918,10 +1918,10 @@
         <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1951,28 +1951,28 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>19</v>
@@ -2008,13 +2008,13 @@
         <v>43</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>28</v>
@@ -2033,19 +2033,19 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2055,51 +2055,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2109,39 +2109,39 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2167,28 +2167,28 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>12</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>2</v>
@@ -2202,12 +2202,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2217,51 +2217,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="J37" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="M37" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2271,51 +2271,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2325,35 +2325,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2379,35 +2379,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G40" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H40" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="I40" s="12" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2418,12 +2418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2433,51 +2433,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J41" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K41" s="12" t="n">
+      <c r="L41" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="M41" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L41" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2487,39 +2487,39 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42" s="12" t="n">
         <v>63</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2566,14 +2566,14 @@
         <v>6</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2599,19 +2599,19 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>4</v>
@@ -2620,7 +2620,7 @@
         <v>4</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>11</v>
@@ -2674,26 +2674,26 @@
         <v>0</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2703,51 +2703,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J46" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K46" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M46" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K46" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L46" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="M46" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>05512</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN PIETRO TERME</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2757,32 +2757,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>1</v>
@@ -2796,12 +2796,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>05512</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>CASTEL SAN PIETRO TERME</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2811,39 +2811,39 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0</v>
@@ -3030,13 +3030,13 @@
         <v>0</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>0</v>
@@ -3246,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>0</v>
@@ -3296,13 +3296,13 @@
         <v>0</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>47</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3352</v>
+        <v>3595</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2488</v>
+        <v>2702</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2362</v>
+        <v>2489</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>756</v>
+        <v>806</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -910,12 +910,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>58414</t>
+          <t>06334</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>VIGNOLA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,35 +925,35 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>22</v>
+        <v>181</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>144</v>
+        <v>214</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>305</v>
+        <v>221</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06334</t>
+          <t>58414</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VIGNOLA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,39 +979,39 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>168</v>
+        <v>23</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>211</v>
+        <v>327</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1033,28 +1033,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>16</v>
@@ -1087,28 +1087,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>11</v>
@@ -1122,12 +1122,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,31 +1141,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>246</v>
+        <v>30</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>182</v>
+        <v>56</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1176,50 +1176,50 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>142</v>
+        <v>246</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>72</v>
+        <v>202</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>98</v>
+        <v>264</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1230,12 +1230,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1245,35 +1245,35 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>230</v>
+        <v>102</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1284,54 +1284,54 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1357,31 +1357,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I21" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>73</v>
-      </c>
       <c r="J21" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1392,12 +1392,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1407,51 +1407,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="I22" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>60</v>
-      </c>
       <c r="J22" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1461,46 +1461,46 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1519,47 +1519,47 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1569,39 +1569,39 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1627,47 +1627,47 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H26" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K26" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K26" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="L26" s="12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1677,39 +1677,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1735,28 +1735,28 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>1</v>
@@ -1770,12 +1770,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06403</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GUASTALLA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1785,51 +1785,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>06403</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>GUASTALLA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1839,39 +1839,39 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1900,13 +1900,13 @@
         <v>49</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>43</v>
@@ -1918,7 +1918,7 @@
         <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>40</v>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>59</v>
@@ -1960,7 +1960,7 @@
         <v>30</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>41</v>
@@ -1969,10 +1969,10 @@
         <v>14</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>19</v>
@@ -2005,31 +2005,31 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2040,12 +2040,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2055,51 +2055,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2109,51 +2109,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="H35" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L35" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>66</v>
-      </c>
       <c r="M35" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2163,51 +2163,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2217,51 +2217,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2271,51 +2271,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,31 +2329,31 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,31 +2383,31 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2418,12 +2418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2433,35 +2433,35 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>0</v>
@@ -2503,23 +2503,23 @@
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2566,14 +2566,14 @@
         <v>6</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2602,13 +2602,13 @@
         <v>22</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>18</v>
@@ -2620,7 +2620,7 @@
         <v>4</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>11</v>
@@ -2634,12 +2634,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05589</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ZOLA PREDOSA</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2649,51 +2649,51 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>05589</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>ZOLA PREDOSA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2703,35 +2703,35 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2761,19 +2761,19 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J47" s="12" t="n">
         <v>2</v>
@@ -2782,7 +2782,7 @@
         <v>6</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>1</v>
@@ -2818,7 +2818,7 @@
         <v>11</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>0</v>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0</v>
@@ -3030,13 +3030,13 @@
         <v>0</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>0</v>
@@ -3246,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3296,13 +3296,13 @@
         <v>0</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>47</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3595</v>
+        <v>3827</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2702</v>
+        <v>2881</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2489</v>
+        <v>2628</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>806</v>
+        <v>869</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>678</v>
+        <v>726</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>316</v>
+        <v>362</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>44</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>6</v>
@@ -1033,31 +1033,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1087,31 +1087,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1141,31 +1141,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1191,51 +1191,51 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
+        <v>126</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>174</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="L18" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="F18" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>246</v>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>202</v>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>264</v>
-      </c>
       <c r="M18" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1245,39 +1245,39 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>44</v>
+        <v>254</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>87</v>
+        <v>224</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1303,16 +1303,16 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>91</v>
@@ -1321,13 +1321,13 @@
         <v>25</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1357,31 +1357,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1411,35 +1411,35 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1465,28 +1465,28 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>1</v>
@@ -1519,28 +1519,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>2</v>
@@ -1573,31 +1573,31 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1627,35 +1627,35 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>81</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>22</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>6</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>71</v>
@@ -1699,17 +1699,17 @@
         <v>13</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>25</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1735,28 +1735,28 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>1</v>
@@ -1789,35 +1789,35 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G29" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="J29" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H29" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="K29" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1843,42 +1843,42 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>41</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1893,46 +1893,46 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1947,35 +1947,35 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -1986,12 +1986,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2001,35 +2001,35 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>39</v>
+        <v>138</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2040,12 +2040,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2055,51 +2055,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J34" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K34" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K34" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="L34" s="12" t="n">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2109,51 +2109,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2163,17 +2163,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
@@ -2182,20 +2182,20 @@
         <v>35</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2221,28 +2221,28 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>11</v>
@@ -2256,12 +2256,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2271,51 +2271,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="H38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="J38" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2332,28 +2332,28 @@
         <v>36</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J39" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2379,35 +2379,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2418,12 +2418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,47 +2437,47 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="G41" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="J41" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2487,51 +2487,51 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J42" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K42" s="12" t="n">
+      <c r="L42" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="M42" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L42" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2541,35 +2541,35 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2580,12 +2580,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2595,51 +2595,51 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2649,39 +2649,39 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="I45" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="J45" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>1</v>
@@ -2782,7 +2782,7 @@
         <v>6</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>1</v>
@@ -2818,7 +2818,7 @@
         <v>11</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>0</v>
@@ -2868,13 +2868,13 @@
         <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>0</v>
@@ -3030,13 +3030,13 @@
         <v>0</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>
@@ -3246,13 +3246,13 @@
         <v>0</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I56" s="12" t="n">
         <v>0</v>
@@ -3296,13 +3296,13 @@
         <v>0</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1026,7 +1026,11 @@
           <t>PIACENZA</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>GIURICIN ANTONIO</t>
@@ -1186,7 +1190,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1564,7 +1568,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1834,7 +1838,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2104,7 +2108,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2158,7 +2162,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2212,7 +2216,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2644,7 +2648,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -525,7 +525,7 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -2912,11 +2912,7 @@
           <t>FIDENZA</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>IACONA GIOVANNI</t>
@@ -2966,11 +2962,7 @@
           <t>MEDICINA</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
@@ -3128,11 +3120,7 @@
           <t>PIANORO</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N57" headerRowCount="1">
-  <autoFilter ref="A10:N57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N58" headerRowCount="1">
+  <autoFilter ref="A10:N58"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,7 +673,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>3827</v>
@@ -3317,6 +3317,60 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>02667</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>PIACENZA</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>GIURICIN ANTONIO</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N58" headerRowCount="1">
-  <autoFilter ref="A10:N58"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O58" headerRowCount="1">
+  <autoFilter ref="A10:O58"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>VIALE EUROPA 111A</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>IACONA GIOVANNI</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>579</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>479</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>474</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>869</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>434</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>204</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>726</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>189</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>VIA M.E.LEPIDO 206</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>388</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>362</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>466</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>323</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>165</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>298</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>VIA PER SPILAMBERTO 1015</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>270</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>234</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>201</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>226</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>236</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>VIA GRAMSCI, 9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>CARCIONE PARIDE</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>248</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>226</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>365</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>VIA FARNESIANA 151</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>GIURICIN ANTONIO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>217</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>264</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>375</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>VIA PIA</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>195</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>228</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>392</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>127</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>233</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>VIA NUOVA BAZZANESE 8</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>138</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>138</v>
       </c>
       <c r="G17" s="12" t="n">
+        <v>138</v>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>266</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>VIA MARTIRI DI CERVAROLO</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>CARCIONE PARIDE</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>VIA SELICE KM. 2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>254</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>224</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>275</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>VIA EMILIA PIACENTINA</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>GIURICIN ANTONIO</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>111</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>VIA MANZONI</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>VIA FERRARESE 166</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>VIA KENNEDY 7</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>CARCIONE PARIDE</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>VIALE DELL'INDUSTRIA 44</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>189</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>VIA TRAVERSETOLO</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>IACONA GIOVANNI</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>VIA PAPA GIOVANNI XXIII</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>GIURICIN ANTONIO</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>VIA BOLOGNA 13</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="H27" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>SS. SUD</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="I28" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="J28" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>VIA SHAKESPEARE SNC</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>VIA CISA LIGURE 10</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>CARCIONE PARIDE</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>VIA STALINGRADO 59/4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="N31" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>VIA ALDINI 186</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>PIETRANTONIO GIULIANO</t>
         </is>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>50</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G32" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>VIA VIGNOLESE 1030</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>138</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="N33" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>VIA G. DOZZA, 33</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="F34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K34" s="12" t="n">
+      <c r="L34" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="M34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2108,42 +2244,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>VIA MANTOVA 109 A</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>IACONA GIOVANNI</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="I35" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>VIA GORIZIA, 25</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>CARCIONE PARIDE</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F36" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H36" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="K36" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K36" s="12" t="n">
+      <c r="L36" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="M36" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="M36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2216,42 +2362,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>S.P PER REGGIO EMILIA 34</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>IACONA GIOVANNI</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="I37" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="J37" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K37" s="12" t="n">
+      <c r="L37" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="M37" s="12" t="n">
+      <c r="N37" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2270,42 +2421,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>VIA CANALETTO, 62</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="J38" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="K38" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K38" s="12" t="n">
+      <c r="L38" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2324,42 +2480,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>COMPLANARE S. LAZZARO SNC</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="I39" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="J39" s="12" t="n">
         <v>26</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L39" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="M39" s="12" t="n">
+      <c r="N39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2378,42 +2539,47 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="J40" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="K40" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K40" s="12" t="n">
+      <c r="L40" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L40" s="12" t="n">
+      <c r="M40" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="M40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2432,42 +2598,47 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>VIA MASSARENTI, 221/3</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="J41" s="12" t="n">
+      <c r="K41" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K41" s="12" t="n">
+      <c r="L41" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="M41" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="M41" s="12" t="n">
+      <c r="N41" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2486,42 +2657,47 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>S.S. 64 LOCALITA' ALTEDO</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="H42" s="12" t="n">
+      <c r="I42" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="I42" s="12" t="n">
+      <c r="J42" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J42" s="12" t="n">
+      <c r="K42" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K42" s="12" t="n">
+      <c r="L42" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="12" t="n">
+      <c r="M42" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="M42" s="12" t="n">
+      <c r="N42" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2540,42 +2716,47 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>VIA GORGHETTO, 2</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="H43" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J43" s="12" t="n">
+      <c r="K43" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K43" s="12" t="n">
+      <c r="L43" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="M43" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="M43" s="12" t="n">
+      <c r="N43" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2594,42 +2775,47 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>TRASVERSALE DI PIANURA</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F44" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H44" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J44" s="12" t="n">
+      <c r="K44" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K44" s="12" t="n">
+      <c r="L44" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L44" s="12" t="n">
+      <c r="M44" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="M44" s="12" t="n">
+      <c r="N44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2648,42 +2834,47 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>VIA FERRARI 38</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>IACONA GIOVANNI</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H45" s="12" t="n">
+      <c r="I45" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="I45" s="12" t="n">
+      <c r="J45" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L45" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M45" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="M45" s="12" t="n">
+      <c r="N45" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2702,42 +2893,47 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>VIA RISORGIMENTO 77</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F46" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H46" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="J46" s="12" t="n">
+      <c r="K46" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K46" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="M46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="N46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2756,42 +2952,47 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>SS MO/SASSUOLO LOC. BAGGIOVARA SNC</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="12" t="n">
+      <c r="I47" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I47" s="12" t="n">
+      <c r="J47" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J47" s="12" t="n">
+      <c r="K47" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K47" s="12" t="n">
+      <c r="L47" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L47" s="12" t="n">
+      <c r="M47" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="M47" s="12" t="n">
+      <c r="N47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2810,42 +3011,47 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>VIA EMILIA PONENTE 210</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="G48" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I48" s="12" t="n">
+      <c r="J48" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J48" s="12" t="n">
+      <c r="K48" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K48" s="12" t="n">
+      <c r="L48" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L48" s="12" t="n">
+      <c r="M48" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="M48" s="12" t="n">
+      <c r="N48" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2862,27 +3068,29 @@
           <t>PARMA</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>VIA EMILIA EST</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>IACONA GIOVANNI</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="G49" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I49" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J49" s="12" t="n">
         <v>0</v>
       </c>
@@ -2895,7 +3103,10 @@
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="N49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2912,21 +3123,23 @@
           <t>FIDENZA</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>VIA XXIV MAGGIO</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>IACONA GIOVANNI</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G50" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H50" s="12" t="n">
         <v>0</v>
       </c>
@@ -2945,7 +3158,10 @@
       <c r="M50" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="N50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2962,21 +3178,23 @@
           <t>MEDICINA</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>VIA S.VITALE OVEST 209</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G51" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H51" s="12" t="n">
         <v>0</v>
       </c>
@@ -2995,7 +3213,10 @@
       <c r="M51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="N51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3014,29 +3235,31 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>TANGENZIALE NORD LUIGI PIRANDELLO 49/51</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G52" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="I52" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J52" s="12" t="n">
         <v>0</v>
       </c>
@@ -3049,7 +3272,10 @@
       <c r="M52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="N52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3068,29 +3294,31 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>REPUBBLICA 12</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>CARCIONE PARIDE</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="G53" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I53" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J53" s="12" t="n">
         <v>0</v>
       </c>
@@ -3103,7 +3331,10 @@
       <c r="M53" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="N53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3120,21 +3351,23 @@
           <t>PIANORO</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>S.S.65 KM.94+340</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G54" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
       </c>
@@ -3153,7 +3386,10 @@
       <c r="M54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="N54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3172,29 +3408,31 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>VIALE D AGOSTINO 141</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="G55" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J55" s="12" t="n">
         <v>0</v>
       </c>
@@ -3207,7 +3445,10 @@
       <c r="M55" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="N55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3226,29 +3467,31 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>VIA PROVINCIALE SUPERIORE</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E56" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="G56" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I56" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J56" s="12" t="n">
         <v>0</v>
       </c>
@@ -3261,7 +3504,10 @@
       <c r="M56" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="N56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3278,27 +3524,29 @@
           <t>PIACENZA</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>VIA CAORSANA</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>GIURICIN ANTONIO</t>
         </is>
       </c>
-      <c r="E57" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="G57" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="I57" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J57" s="12" t="n">
         <v>0</v>
       </c>
@@ -3311,7 +3559,10 @@
       <c r="M57" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="N57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3330,17 +3581,19 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>VIA MANFREDI 74</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>GIURICIN ANTONIO</t>
         </is>
       </c>
-      <c r="E58" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F58" s="12" t="n">
         <v>0</v>
       </c>
@@ -3365,7 +3618,10 @@
       <c r="M58" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="N58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3827</v>
+        <v>3996</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2881</v>
+        <v>2992</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2628</v>
+        <v>2740</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>579</v>
+        <v>608</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>869</v>
+        <v>927</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>726</v>
+        <v>756</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>6</v>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>12</v>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H17" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="L17" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="J17" s="12" t="n">
+      <c r="M17" s="12" t="n">
+        <v>274</v>
+      </c>
+      <c r="N17" s="12" t="n">
         <v>106</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L17" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>266</v>
-      </c>
-      <c r="N17" s="12" t="n">
-        <v>103</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>8</v>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>91</v>
@@ -1391,13 +1391,13 @@
         <v>25</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06210</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CARPI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA MANZONI</t>
+          <t>VIA FERRARESE 166</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>06210</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>CARPI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARESE 166</t>
+          <t>VIA MANZONI</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M22" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="G22" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="M22" s="12" t="n">
-        <v>100</v>
-      </c>
       <c r="N22" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>1</v>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>2</v>
@@ -1671,13 +1671,13 @@
         <v>82</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>75</v>
@@ -1689,128 +1689,128 @@
         <v>12</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XXIII</t>
+          <t>VIA BOLOGNA 13</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
         <v>78</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K26" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L26" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L26" s="12" t="n">
-        <v>23</v>
-      </c>
       <c r="M26" s="12" t="n">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA BOLOGNA 13</t>
+          <t>VIA PAPA GIOVANNI XXIII</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,16 +1845,16 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>35</v>
@@ -1863,13 +1863,13 @@
         <v>9</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>45</v>
@@ -1922,13 +1922,13 @@
         <v>13</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,16 +1963,16 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>49</v>
@@ -1981,13 +1981,13 @@
         <v>20</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>14</v>
@@ -2043,14 +2043,14 @@
         <v>11</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>20</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2081,19 +2081,19 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>21</v>
@@ -2102,10 +2102,10 @@
         <v>6</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>2</v>
@@ -2175,135 +2175,135 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>VIA MANTOVA 109 A</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA MANTOVA 109 A</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA GORIZIA, 25</t>
+          <t>S.P PER REGGIO EMILIA 34</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,56 +2313,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H36" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="J36" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>35</v>
-      </c>
       <c r="K36" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>S.P PER REGGIO EMILIA 34</t>
+          <t>VIA GORIZIA, 25</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,39 +2372,39 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
         <v>43</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2435,19 +2435,19 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>71</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>13</v>
@@ -2456,7 +2456,7 @@
         <v>6</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>13</v>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COMPLANARE S. LAZZARO SNC</t>
+          <t>VIA MASSARENTI, 221/3</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2494,52 +2494,52 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO 36</t>
+          <t>S.S. 64 LOCALITA' ALTEDO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,35 +2549,35 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2588,17 +2588,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA MASSARENTI, 221/3</t>
+          <t>COMPLANARE S. LAZZARO SNC</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2612,52 +2612,52 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>S.S. 64 LOCALITA' ALTEDO</t>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,35 +2667,35 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>26</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>21</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2810,10 +2810,10 @@
         <v>6</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>22</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>2</v>
@@ -2869,7 +2869,7 @@
         <v>4</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>12</v>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
@@ -2969,7 +2969,7 @@
         <v>14</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>1</v>
@@ -2987,10 +2987,10 @@
         <v>6</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>11</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>0</v>
@@ -3252,13 +3252,13 @@
         <v>0</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="J52" s="12" t="n">
         <v>0</v>
@@ -3539,13 +3539,13 @@
         <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3996</v>
+        <v>4179</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2992</v>
+        <v>3118</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2740</v>
+        <v>2868</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>503</v>
+        <v>540</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>927</v>
+        <v>988</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>756</v>
+        <v>800</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>45</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>105</v>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
+        <v>267</v>
+      </c>
+      <c r="G14" s="12" t="n">
         <v>259</v>
       </c>
-      <c r="G14" s="12" t="n">
-        <v>242</v>
-      </c>
       <c r="H14" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>6</v>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>419</v>
+        <v>450</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>38</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>06210</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>CARPI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARESE 166</t>
+          <t>VIA MANZONI</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
         <v>106</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H21" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="K21" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>37</v>
-      </c>
       <c r="L21" s="12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>06210</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CARPI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA MANZONI</t>
+          <t>VIA FERRARESE 166</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY 7</t>
+          <t>VIA BOLOGNA 13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,56 +1546,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIA KENNEDY 7</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,153 +1605,153 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="K24" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="L24" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L24" s="12" t="n">
-        <v>42</v>
-      </c>
       <c r="M24" s="12" t="n">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA TRAVERSETOLO</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>86</v>
+        <v>152</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>49</v>
+        <v>176</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>140</v>
+        <v>205</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA BOLOGNA 13</t>
+          <t>VIA TRAVERSETOLO</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,16 +1786,16 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>28</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>57</v>
@@ -1804,13 +1804,13 @@
         <v>14</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SS. SUD</t>
+          <t>VIA SHAKESPEARE SNC</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA SHAKESPEARE SNC</t>
+          <t>SS. SUD</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,32 +1900,32 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>3</v>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>30</v>
@@ -2040,10 +2040,10 @@
         <v>14</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>20</v>
@@ -2081,16 +2081,16 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>37</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>47</v>
@@ -2099,72 +2099,72 @@
         <v>21</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>41</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA VIGNOLESE 1030</t>
+          <t>VIA MANTOVA 109 A</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="H33" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L33" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>124</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="M33" s="12" t="n">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,55 +2175,55 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA MANTOVA 109 A</t>
+          <t>VIA VIGNOLESE 1030</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>47</v>
+        <v>155</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>0</v>
@@ -2276,17 +2276,17 @@
         <v>16</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>11</v>
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>0</v>
@@ -2394,34 +2394,34 @@
         <v>5</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA CANALETTO, 62</t>
+          <t>VIA MASSARENTI, 221/3</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,56 +2431,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA MASSARENTI, 221/3</t>
+          <t>VIA CANALETTO, 62</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,23 +2490,23 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>13</v>
@@ -2515,14 +2515,14 @@
         <v>6</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2553,31 +2553,31 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>9</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>2</v>
@@ -2674,7 +2674,7 @@
         <v>37</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>1</v>
@@ -2692,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>0</v>
@@ -2730,35 +2730,35 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2789,31 +2789,31 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2851,13 +2851,13 @@
         <v>22</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>18</v>
@@ -2869,7 +2869,7 @@
         <v>4</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>12</v>
@@ -2907,19 +2907,19 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>6</v>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
@@ -2969,7 +2969,7 @@
         <v>14</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>1</v>
@@ -2987,7 +2987,7 @@
         <v>6</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>3</v>
@@ -3252,13 +3252,13 @@
         <v>0</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="J52" s="12" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
@@ -3539,13 +3539,13 @@
         <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>0</v>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>VIA MANFREDI 74</t>
+          <t>VIA MANFREDI 74 IMP. 2667</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3616,14 +3616,14 @@
         <v>0</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4179</v>
+        <v>4379</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3118</v>
+        <v>3266</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2868</v>
+        <v>3047</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>621</v>
+        <v>648</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>516</v>
+        <v>551</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>988</v>
+        <v>1042</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>800</v>
+        <v>842</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>398</v>
+        <v>449</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>263</v>
+        <v>312</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>49</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>6</v>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>10</v>
@@ -1290,55 +1290,55 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA SELICE KM. 2</t>
+          <t>VIA EMILIA PIACENTINA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>257</v>
+        <v>170</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>250</v>
+        <v>106</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="L19" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="M19" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="N19" s="12" t="n">
         <v>39</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>289</v>
-      </c>
-      <c r="N19" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1349,55 +1349,55 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA PIACENTINA</t>
+          <t>VIA SELICE KM. 2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>162</v>
+        <v>259</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>96</v>
+        <v>261</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>123</v>
+        <v>298</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G22" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J22" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="H22" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>84</v>
-      </c>
       <c r="K22" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>71</v>
@@ -1562,40 +1562,40 @@
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY 7</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,157 +1605,157 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>84</v>
+        <v>189</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIA TRAVERSETOLO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>176</v>
+        <v>55</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>205</v>
+        <v>158</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA TRAVERSETOLO</t>
+          <t>VIA KENNEDY 7</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1786,16 +1786,16 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>28</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>57</v>
@@ -1804,13 +1804,13 @@
         <v>14</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1848,13 +1848,13 @@
         <v>77</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>47</v>
@@ -1866,14 +1866,14 @@
         <v>30</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,19 +1904,19 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>9</v>
@@ -1925,7 +1925,7 @@
         <v>38</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>3</v>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA STALINGRADO 59/4</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2022,35 +2022,35 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>41</v>
@@ -2116,55 +2116,55 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA MANTOVA 109 A</t>
+          <t>VIA VIGNOLESE 1030</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>55</v>
+        <v>169</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,55 +2175,55 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA VIGNOLESE 1030</t>
+          <t>VIA MANTOVA 109 A</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="H34" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L34" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="M34" s="12" t="n">
-        <v>155</v>
+        <v>64</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2258,35 +2258,35 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2317,31 +2317,31 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2376,35 +2376,35 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2435,35 +2435,35 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2494,19 +2494,19 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>13</v>
@@ -2515,10 +2515,10 @@
         <v>6</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2553,28 +2553,28 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>7</v>
@@ -2612,16 +2612,16 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>28</v>
@@ -2630,13 +2630,13 @@
         <v>10</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2674,13 +2674,13 @@
         <v>37</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>8</v>
@@ -2692,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>0</v>
@@ -2730,22 +2730,22 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>4</v>
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>7</v>
@@ -2810,14 +2810,14 @@
         <v>9</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2848,19 +2848,19 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>4</v>
@@ -2869,10 +2869,10 @@
         <v>4</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2883,17 +2883,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05589</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ZOLA PREDOSA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIA RISORGIMENTO 77</t>
+          <t>SS MO/SASSUOLO LOC. BAGGIOVARA SNC</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,56 +2903,56 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>05589</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>ZOLA PREDOSA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>SS MO/SASSUOLO LOC. BAGGIOVARA SNC</t>
+          <t>VIA RISORGIMENTO 77</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,39 +2962,39 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K47" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="J47" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K47" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L47" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
         <v>11</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>0</v>
@@ -3252,13 +3252,13 @@
         <v>0</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="J52" s="12" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
@@ -3539,13 +3539,13 @@
         <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4379</v>
+        <v>4518</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3266</v>
+        <v>3382</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3047</v>
+        <v>3134</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>648</v>
+        <v>662</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>577</v>
+        <v>613</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>551</v>
+        <v>570</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1042</v>
+        <v>1095</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>842</v>
+        <v>874</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>49</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>74</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>40</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>10</v>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1376,13 +1376,13 @@
         <v>130</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>93</v>
@@ -1394,7 +1394,7 @@
         <v>41</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>8</v>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G21" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="H21" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>79</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>98</v>
-      </c>
       <c r="K21" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,16 +1491,16 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>86</v>
@@ -1509,13 +1509,13 @@
         <v>38</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,170 +1550,170 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>71</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIA TRAVERSETOLO</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="J24" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="G24" s="12" t="n">
-        <v>169</v>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>99</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>189</v>
-      </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>166</v>
+      </c>
+      <c r="N24" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="K24" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>211</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA TRAVERSETOLO</t>
+          <t>VIA KENNEDY 7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY 7</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,39 +1723,39 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>28</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>14</v>
@@ -1807,7 +1807,7 @@
         <v>26</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>9</v>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1904,35 +1904,35 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>54</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,52 +2022,52 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA ALDINI 186</t>
+          <t>VIA VIGNOLESE 1030</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>97</v>
+        <v>182</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA VIGNOLESE 1030</t>
+          <t>VIA ALDINI 186</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2140,31 +2140,31 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2199,28 +2199,28 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>7</v>
@@ -2234,55 +2234,55 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA STALINGRADO 59/4</t>
+          <t>S.P PER REGGIO EMILIA 34</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L35" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="N35" s="12" t="n">
         <v>12</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>130</v>
-      </c>
-      <c r="N35" s="12" t="n">
-        <v>20</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2293,55 +2293,55 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>S.P PER REGGIO EMILIA 34</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2376,35 +2376,35 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2435,19 +2435,19 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="12" t="n">
         <v>45</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>43</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>15</v>
@@ -2456,14 +2456,14 @@
         <v>7</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2497,13 +2497,13 @@
         <v>43</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>36</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>41</v>
@@ -2556,13 +2556,13 @@
         <v>43</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>34</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>27</v>
@@ -2574,7 +2574,7 @@
         <v>16</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>7</v>
@@ -2612,19 +2612,19 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>10</v>
@@ -2633,7 +2633,7 @@
         <v>10</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>4</v>
@@ -2674,7 +2674,7 @@
         <v>37</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>1</v>
@@ -2692,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>0</v>
@@ -2751,14 +2751,14 @@
         <v>4</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
         <v>9</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>4</v>
@@ -2848,19 +2848,19 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>51</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>4</v>
@@ -2869,7 +2869,7 @@
         <v>4</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>13</v>
@@ -2910,7 +2910,7 @@
         <v>17</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>1</v>
@@ -2928,7 +2928,7 @@
         <v>7</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>4</v>
@@ -2987,14 +2987,14 @@
         <v>0</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
         <v>11</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>0</v>
@@ -3252,13 +3252,13 @@
         <v>0</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="J52" s="12" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>0</v>
@@ -3425,13 +3425,13 @@
         <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J55" s="12" t="n">
         <v>0</v>
@@ -3539,13 +3539,13 @@
         <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4518</v>
+        <v>4778</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3382</v>
+        <v>3580</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3134</v>
+        <v>3315</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>662</v>
+        <v>697</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1095</v>
+        <v>1149</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>491</v>
+        <v>520</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>874</v>
+        <v>927</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="I12" s="12" t="n">
+        <v>219</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>399</v>
+      </c>
+      <c r="K12" s="12" t="n">
         <v>201</v>
       </c>
-      <c r="J12" s="12" t="n">
-        <v>381</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>194</v>
-      </c>
       <c r="L12" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>466</v>
+        <v>492</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>6</v>
@@ -1054,55 +1054,55 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>53958</t>
+          <t>06249</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>PIACENZA</t>
+          <t>SASSUOLO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA FARNESIANA 151</t>
+          <t>VIA PIA</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>334</v>
+        <v>303</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>14</v>
+        <v>347</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>36</v>
+        <v>516</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>459</v>
+        <v>317</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,55 +1113,55 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>06249</t>
+          <t>53958</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SASSUOLO</t>
+          <t>PIACENZA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA PIA</t>
+          <t>VIA FARNESIANA 151</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>293</v>
+        <v>349</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>328</v>
+        <v>16</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>501</v>
+        <v>39</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>294</v>
+        <v>478</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>41</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>93</v>
@@ -1391,17 +1391,17 @@
         <v>52</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>71</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>30</v>
@@ -1585,135 +1585,135 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA TRAVERSETOLO</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="G24" s="12" t="n">
+        <v>182</v>
+      </c>
+      <c r="H24" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="H24" s="12" t="n">
-        <v>88</v>
-      </c>
       <c r="I24" s="12" t="n">
-        <v>61</v>
+        <v>214</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY 7</t>
+          <t>VIA TRAVERSETOLO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIA KENNEDY 7</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,35 +1723,35 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>209</v>
+        <v>118</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,135 +1762,135 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XXIII</t>
+          <t>SS. SUD</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA SHAKESPEARE SNC</t>
+          <t>VIA PAPA GIOVANNI XXIII</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="H28" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="K28" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="L28" s="12" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>SS. SUD</t>
+          <t>VIA SHAKESPEARE SNC</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,39 +1900,39 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1963,25 +1963,25 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>21</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>94</v>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>VIA VIGNOLESE 1030</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>51</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA VIGNOLESE 1030</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,39 +2077,39 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="K32" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L32" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L32" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="M32" s="12" t="n">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>41</v>
@@ -2175,55 +2175,55 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA MANTOVA 109 A</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>12</v>
@@ -2293,76 +2293,76 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA STALINGRADO 59/4</t>
+          <t>VIA GORIZIA, 25</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>43</v>
       </c>
       <c r="K36" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L36" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L36" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="M36" s="12" t="n">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA GORIZIA, 25</t>
+          <t>VIA MANTOVA 109 A</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,39 +2372,39 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2435,31 +2435,31 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA CANALETTO, 62</t>
+          <t>S.S. 64 LOCALITA' ALTEDO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2494,31 +2494,31 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I39" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M39" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="N39" s="12" t="n">
         <v>7</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>115</v>
-      </c>
-      <c r="N39" s="12" t="n">
-        <v>14</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2529,17 +2529,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>S.S. 64 LOCALITA' ALTEDO</t>
+          <t>VIA CANALETTO, 62</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2556,28 +2556,28 @@
         <v>43</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2612,16 +2612,16 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>29</v>
@@ -2630,10 +2630,10 @@
         <v>10</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>4</v>
@@ -2674,7 +2674,7 @@
         <v>37</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>1</v>
@@ -2692,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>0</v>
@@ -2733,7 +2733,7 @@
         <v>30</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>24</v>
@@ -2751,14 +2751,14 @@
         <v>4</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2810,14 +2810,14 @@
         <v>9</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2848,19 +2848,19 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>4</v>
@@ -2869,10 +2869,10 @@
         <v>4</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2907,13 +2907,13 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" s="12" t="n">
         <v>6</v>
@@ -2925,13 +2925,13 @@
         <v>2</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2966,19 +2966,19 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>6</v>
@@ -2987,7 +2987,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>11</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>0</v>
@@ -3060,72 +3060,76 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>02945</t>
+          <t>02667</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>PIACENZA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA EST</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
+          <t>VIA MANFREDI 74 IMP. 2667</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02970</t>
+          <t>02945</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>FIDENZA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA XXIV MAGGIO</t>
+          <t>VIA EMILIA EST</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -3138,13 +3142,13 @@
         <v>0</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>0</v>
@@ -3163,37 +3167,37 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>05511</t>
+          <t>02970</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>MEDICINA</t>
+          <t>FIDENZA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>VIA S.VITALE OVEST 209</t>
+          <t>VIA XXIV MAGGIO</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H51" s="12" t="n">
         <v>0</v>
@@ -3225,40 +3229,36 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>06353</t>
+          <t>05511</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>MEDICINA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE NORD LUIGI PIRANDELLO 49/51</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+          <t>VIA S.VITALE OVEST 209</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="J52" s="12" t="n">
         <v>0</v>
@@ -3277,24 +3277,24 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>06408</t>
+          <t>06353</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CORREGGIO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>REPUBBLICA 12</t>
+          <t>TANGENZIALE NORD LUIGI PIRANDELLO 49/51</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3304,20 +3304,20 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>0</v>
@@ -3343,36 +3343,40 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>15548</t>
+          <t>06408</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>PIANORO</t>
+          <t>CORREGGIO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>S.S.65 KM.94+340</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr"/>
+          <t>REPUBBLICA 12</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="12" t="n">
         <v>0</v>
@@ -3391,31 +3395,27 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>15552</t>
+          <t>15548</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>PIANORO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIALE D AGOSTINO 141</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+          <t>S.S.65 KM.94+340</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
@@ -3425,13 +3425,13 @@
         <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J55" s="12" t="n">
         <v>0</v>
@@ -3450,24 +3450,24 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>15552</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>MOLINELLA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE SUPERIORE</t>
+          <t>VIALE D AGOSTINO 141</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3477,20 +3477,20 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="H56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J56" s="12" t="n">
         <v>0</v>
@@ -3516,36 +3516,40 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>52082</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>PIACENZA</t>
+          <t>MOLINELLA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>VIA CAORSANA</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>VIA PROVINCIALE SUPERIORE</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>187</v>
+        <v>3</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>0</v>
@@ -3571,7 +3575,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>02667</t>
+          <t>52082</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3581,14 +3585,10 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>VIA MANFREDI 74 IMP. 2667</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+          <t>VIA CAORSANA</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
           <t>GIURICIN ANTONIO</t>
@@ -3598,13 +3598,13 @@
         <v>0</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="H58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="J58" s="12" t="n">
         <v>0</v>
@@ -3616,14 +3616,14 @@
         <v>0</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4778</v>
+        <v>5006</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3580</v>
+        <v>3758</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3315</v>
+        <v>3509</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>697</v>
+        <v>724</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>633</v>
+        <v>668</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>592</v>
+        <v>622</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1149</v>
+        <v>1204</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>927</v>
+        <v>977</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>492</v>
+        <v>527</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>19</v>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>42</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>13</v>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>32</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARESE 166</t>
+          <t>VIA BOLOGNA 13</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>122</v>
+        <v>204</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,66 +1526,66 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA BOLOGNA 13</t>
+          <t>VIA TRAVERSETOLO</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIA FERRARESE 166</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1609,94 +1609,94 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>232</v>
+        <v>126</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA TRAVERSETOLO</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>68</v>
+        <v>230</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>175</v>
+        <v>246</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>101</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>33</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>78</v>
@@ -1748,10 +1748,10 @@
         <v>20</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SS. SUD</t>
+          <t>VIA SHAKESPEARE SNC</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,157 +1782,157 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
         <v>85</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XXIII</t>
+          <t>SS. SUD</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA SHAKESPEARE SNC</t>
+          <t>VIA PAPA GIOVANNI XXIII</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="H29" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="K29" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="L29" s="12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>24</v>
@@ -1984,10 +1984,10 @@
         <v>16</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2025,13 +2025,13 @@
         <v>71</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>32</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>51</v>
@@ -2043,7 +2043,7 @@
         <v>21</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>4</v>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA ALDINI 186</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,35 +2136,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>105</v>
+        <v>160</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,55 +2175,55 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA STALINGRADO 59/4</t>
+          <t>S.P PER REGGIO EMILIA 34</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,55 +2234,55 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>S.P PER REGGIO EMILIA 34</t>
+          <t>VIA ALDINI 186</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>9</v>
@@ -2338,7 +2338,7 @@
         <v>14</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>4</v>
@@ -2376,28 +2376,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>7</v>
@@ -2435,35 +2435,35 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2494,28 +2494,28 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>7</v>
@@ -2553,28 +2553,28 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I40" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="K40" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L40" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J40" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K40" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L40" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M40" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>14</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>4</v>
@@ -2674,13 +2674,13 @@
         <v>37</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>8</v>
@@ -2692,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>0</v>
@@ -2730,28 +2730,28 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>2</v>
@@ -2789,28 +2789,28 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>4</v>
@@ -2848,22 +2848,22 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>4</v>
@@ -2907,28 +2907,28 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>5</v>
@@ -2966,19 +2966,19 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>6</v>
@@ -2987,7 +2987,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>11</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>0</v>
@@ -3084,31 +3084,31 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="N49" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="G49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K49" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N49" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3311,13 +3311,13 @@
         <v>0</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>0</v>
@@ -3484,13 +3484,13 @@
         <v>0</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J56" s="12" t="n">
         <v>0</v>
@@ -3598,13 +3598,13 @@
         <v>0</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="H58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="J58" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - SAGLIMBENI GIUSEPPE CRISTIAN.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5006</v>
+        <v>5214</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3758</v>
+        <v>3937</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3509</v>
+        <v>3731</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>724</v>
+        <v>751</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>622</v>
+        <v>672</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1204</v>
+        <v>1280</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>538</v>
+        <v>560</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>977</v>
+        <v>1030</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>581</v>
+        <v>596</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>527</v>
+        <v>561</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>536</v>
+        <v>569</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>87</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>43</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,52 +1314,52 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>32</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>06210</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>CARPI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA SELICE KM. 2</t>
+          <t>VIA MANZONI</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>272</v>
+        <v>30</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>305</v>
+        <v>102</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>331</v>
+        <v>139</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06210</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CARPI</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA MANZONI</t>
+          <t>VIA SELICE KM. 2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>28</v>
+        <v>287</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>93</v>
+        <v>317</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>134</v>
+        <v>358</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,35 +1491,35 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>71</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1550,35 +1550,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>41</v>
@@ -1630,7 +1630,7 @@
         <v>23</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>43</v>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>19</v>
@@ -1689,10 +1689,10 @@
         <v>54</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>2</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>34</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>5</v>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>11</v>
@@ -1866,7 +1866,7 @@
         <v>41</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>4</v>
@@ -1904,19 +1904,19 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>14</v>
@@ -1925,7 +1925,7 @@
         <v>26</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>10</v>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>16</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>21</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,59 +2057,59 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>S.P PER REGGIO EMILIA 34</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>1</v>
+        <v>154</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>33</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>23</v>
@@ -2175,114 +2175,114 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>S.P PER REGGIO EMILIA 34</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>104</v>
+        <v>157</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA ALDINI 186</t>
+          <t>VIA MANTOVA 109 A</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="L35" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="N35" s="12" t="n">
         <v>7</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>106</v>
-      </c>
-      <c r="N35" s="12" t="n">
-        <v>41</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2293,76 +2293,76 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA GORIZIA, 25</t>
+          <t>VIA ALDINI 186</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA MANTOVA 109 A</t>
+          <t>VIA GORIZIA, 25</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,39 +2372,39 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>143</v>
+        <v>6</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2435,35 +2435,35 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2494,28 +2494,28 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>7</v>
@@ -2553,19 +2553,19 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>16</v>
@@ -2574,7 +2574,7 @@
         <v>7</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>14</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>4</v>
@@ -2647,17 +2647,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO 36</t>
+          <t>VIA GORGHETTO, 2</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,56 +2667,56 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="K42" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L42" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M42" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="N42" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L42" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA GORGHETTO, 2</t>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,157 +2726,157 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G43" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J43" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K43" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H43" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="K43" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="L43" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>TRASVERSALE DI PIANURA</t>
+          <t>VIA FERRARI 38</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARI 38</t>
+          <t>TRASVERSALE DI PIANURA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K45" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L45" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M45" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="N45" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L45" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M45" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="N45" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
         <v>23</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>2</v>
@@ -2928,7 +2928,7 @@
         <v>12</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>5</v>
@@ -2966,19 +2966,19 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>6</v>
@@ -2987,14 +2987,14 @@
         <v>0</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3084,35 +3084,35 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K49" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K49" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3311,13 +3311,13 @@
         <v>0</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>0</v>
@@ -3484,13 +3484,13 @@
         <v>0</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="H56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="J56" s="12" t="n">
         <v>0</v>
@@ -3598,13 +3598,13 @@
         <v>0</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="J58" s="12" t="n">
         <v>0</v>
